--- a/data_extactor/batch_10_fa/trimmed/batch_0017_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0017_fa_trim.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>نگارش | تفکر انتقادی | درک مطلب | شنیدن فعال | سخن گفتن | یادگیری فعال | نظارت | ریاضیات | استراتژی‌های یادگیری | علوم پایه</t>
+          <t>نگارش | تفکر انتقادی | درک مطلب | گوش دادن فعال | سخن گفتن | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,7 +518,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان کتبی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>درک کتبی | بیان کتبی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان فناوری مهندسی برق و الکترونیک | نقشه‌کش‌های برق و الکترونیک | تعمیرکاران تجهیزات تجاری و صنعتی برق و الکترونیک | تعمیرکاران برق و الکترونیک نیروگاه، پست برق و رله | مهندسان الکترونیک، به‌جز کامپیوتر | مهندسان مکاترونیک | مهندسان سامانه‌های انرژی خورشیدی</t>
+          <t>کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | نقشه‌کشان برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | تعمیرکار تجهیزات الکتریکی نیروگاه، پست برق و رله | مهندسان الکترونیک، به‌جز کامپیوتر | مهندسان مکاترونیک | مهندسان سیستم‌های انرژی خورشیدی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | سخن گفتن | شنیدن فعال | نگارش | ریاضیات | نظارت | یادگیری فعال | استراتژی‌های یادگیری | علوم پایه</t>
+          <t>درک مطلب | تفکر انتقادی | سخن گفتن | گوش دادن فعال | نگارش | ریاضیات | نظارت | یادگیری فعال | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,7 +575,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>بیان شفاهی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | درک شفاهی | درک کتبی | حساسیت به مسئله</t>
+          <t>بیان شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | درک شفاهی | درک کتبی | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مهندسان سخت‌افزار کامپیوتر | مهندسان برق | تکنسین‌ها و کارشناسان فناوری مهندسی برق و الکترونیک | نقشه‌کش‌های برق و الکترونیک | تکنسین‌ها و کارشناسان فناوری الکترومکانیک و مکاترونیک | مهندسان مکاترونیک | مهندسان رباتیک</t>
+          <t>مهندسان سخت‌افزار رایانه | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | نقشه‌کشان برق و الکترونیک | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان مکاترونیک | مهندسان رباتیک</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | سخن گفتن | درک مطلب | نگارش | یادگیری فعال | نظارت</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | درک مطلب | نگارش | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,7 +632,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | درک شفاهی | حساسیت به مسئله | درک کتبی | استدلال استقرایی | مرتب‌سازی اطلاعات | بیان شفاهی</t>
+          <t>استدلال قیاسی | درک شفاهی | حساسیت به مسئله | درک کتبی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بیان شفاهی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مهندسان سخت‌افزار کامپیوتر | معماران شبکه‌های کامپیوتری | تکنسین‌ها و کارشناسان فناوری مهندسی برق و الکترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | مهندسان مکاترونیک | نصابان و تعمیرکاران تجهیزات رادیویی، سلولی و دکل‌های مخابراتی | متخصصان مهندسی مخابرات</t>
+          <t>مهندسان سخت‌افزار رایانه | معماران شبکه رایانه‌ای | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | مهندسان مکاترونیک | نصابان و تعمیرکاران تجهیزات رادیویی، سلولار و دکل‌های مخابراتی | متخصصان مهندسی مخابرات</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,12 +679,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | یادگیری فعال | ریاضیات | علوم پایه | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | نظارت | تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | یادگیری فعال | ریاضیات | علوم | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | طراحی | شیمی | ریاضیات | ساختمان و سازه | زیست‌شناسی | حقوق و امور دولتی</t>
+          <t>مهندسی و فناوری | طراحی | شیمی | ریاضیات | ساختمان و ساخت‌وساز | زیست‌شناسی | قانون و دولت</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مهندسان عمران | دانشمندان حفاظت از منابع طبیعی | بازرسان انطباق زیست‌محیطی | تکنسین‌ها و کارشناسان فناوری مهندسی محیط‌زیست | دانشمندان و متخصصان محیط‌زیست، شامل بهداشت | هیدرولوژیست‌ها | مهندسان آب و فاضلاب</t>
+          <t>مهندسان عمران | دانشمندان حفاظت از منابع طبیعی | بازرسان رعایت ضوابط زیست‌محیطی | کارشناسان و تکنسین‌های مهندسی محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | آب‌شناسان و هیدرولوژیست‌ها | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | نگارش | تفکر انتقادی | سخن گفتن | نظارت | استراتژی‌های یادگیری | یادگیری فعال</t>
+          <t>درک مطلب | گوش دادن فعال | نگارش | تفکر انتقادی | سخن گفتن | نظارت | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | ایمنی و امنیت عمومی | حقوق و امور دولتی | آموزش و تدریس | مکانیک | شیمی</t>
+          <t>مهندسی و فناوری | ایمنی و امنیت عمومی | قانون و دولت | آموزش و پرورش | مکانیک | شیمی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مدیران انطباق و رعایت قوانین | بازرسان ساختمان و سازه | مهندسان محیط‌زیست | مهندسان پیشگیری و حفاظت از حریق | مهندسان صنایع | متخصصان بهداشت و ایمنی حرفه‌ای | تکنسین‌های بهداشت و ایمنی حرفه‌ای</t>
+          <t>مدیران تطبیق و نظارت مقرراتی | بازرسان ساخت‌وساز و ساختمان | مهندسان محیط‌زیست | مهندسان پیشگیری و حفاظت از حریق | مهندسان صنایع | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کاردان‌ها و تکنسین‌های بهداشت حرفه‌ای و ایمنی کار</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | درک مطلب | شنیدن فعال | نگارش | یادگیری فعال | علوم پایه | ریاضیات | استراتژی‌های یادگیری | نظارت</t>
+          <t>تفکر انتقادی | سخن گفتن | درک مطلب | گوش دادن فعال | نگارش | یادگیری فعال | علوم | ریاضیات | راهبردهای یادگیری | نظارت</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | ساختمان و سازه | طراحی | ایمنی و امنیت عمومی | ریاضیات | فیزیک | شیمی</t>
+          <t>مهندسی و فناوری | ساختمان و ساخت‌وساز | طراحی | ایمنی و امنیت عمومی | ریاضیات | فیزیک | شیمی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | بیان کتبی | مرتب‌سازی اطلاعات</t>
+          <t>حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | بیان کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مهندسان عمران | بازرسان ساختمان و سازه | بازرسان و کارشناسان بررسی حریق | آتش‌نشانان | سرپرستان رده‌اول کارکنان آتش‌نشانی و پیشگیری از حریق | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | نصابان سامانه‌های اعلام و اطفای حریق و دزدگیر</t>
+          <t>مهندسان عمران | بازرسان ساخت‌وساز و ساختمان | بازرسان و کارشناسان بررسی علل حریق | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | نصاب سیستم‌های اعلام سرقت و حریق</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,12 +850,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | درک مطلب | سخن گفتن | نگارش | نظارت | ریاضیات | یادگیری فعال</t>
+          <t>تفکر انتقادی | گوش دادن فعال | درک مطلب | سخن گفتن | نگارش | نظارت | ریاضیات | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | تولید و فرآوری | مکانیک | طراحی | ریاضیات | رایانه و الکترونیک | مدیریت و امور اداری</t>
+          <t>مهندسی و فناوری | تولید و فرآوری | مکانیک | طراحی | ریاضیات | رایانه و الکترونیک | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مهندسان عوامل انسانی و ارگونومی | تکنسین‌ها و کارشناسان فناوری مهندسی صنایع | مدیران تولید صنعتی | مهندسان لجستیک | مهندسان تولید و ساخت | مهندسان مکانیک | مدیران سیستم‌های کنترل کیفیت</t>
+          <t>مهندسان عوامل انسانی و ارگونومی | کارشناسان و تکنسین‌های مهندسی صنایع | مدیران تولید صنعتی | مهندسان لجستیک و زنجیره تأمین | مهندسان تولید و ساخت | مهندسان مکانیک | مدیران سیستم‌های کنترل کیفیت</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | نگارش | شنیدن فعال | درک مطلب | یادگیری فعال | نظارت | ریاضیات | استراتژی‌های یادگیری | علوم پایه</t>
+          <t>تفکر انتقادی | سخن گفتن | نگارش | گوش دادن فعال | درک مطلب | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مهندسان زیستی و پزشکی | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | مهندسان صنایع | مهندسان تولید و ساخت | مهندسان مکانیک | متخصصان بهداشت و ایمنی حرفه‌ای | مهندسان رباتیک</t>
+          <t>مهندسان پزشکی و بیوانجینیرینگ | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | مهندسان صنایع | مهندسان تولید و ساخت | مهندسان مکانیک | کارشناسان بهداشت حرفه‌ای و ایمنی کار | مهندسان رباتیک</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | تفکر انتقادی | نگارش | شنیدن فعال | نظارت | علوم پایه | یادگیری فعال | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | سخن گفتن | تفکر انتقادی | نگارش | گوش دادن فعال | نظارت | علوم | یادگیری فعال | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان کتبی | استدلال قیاسی | درک شفاهی | حساسیت به مسئله | استدلال استقرایی | مرتب‌سازی اطلاعات</t>
+          <t>درک کتبی | بیان کتبی | استدلال قیاسی | درک شفاهی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان فناوری کالیبراسیون | تکنسین‌ها و کارشناسان فناوری مهندسی صنایع | مهندسان صنایع | مهندسان تولید و ساخت | تحلیل‌گران کنترل کیفیت | مدیران سیستم‌های کنترل کیفیت | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار</t>
+          <t>تکنسین‌ها و کارشناسان فنی کالیبراسیون | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان تولید و ساخت | کارشناسان تحلیل کنترل کیفیت | مدیران سیستم‌های کنترل کیفیت | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>ریاضیات | درک مطلب | سخن گفتن | نظارت | شنیدن فعال | نگارش | تفکر انتقادی | یادگیری فعال | استراتژی‌های یادگیری | علوم پایه</t>
+          <t>ریاضیات | درک مطلب | سخن گفتن | نظارت | گوش دادن فعال | نگارش | تفکر انتقادی | یادگیری فعال | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>تجسم فضایی | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک کتبی | مرتب‌سازی اطلاعات</t>
+          <t>تجسم | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تکنسین‌ها و کارشناسان فناوری مهندسی صنایع | مهندسان صنایع | مدیران تولید صنعتی | مهندسان مواد | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان اعتبارسنجی و صحه‌گذاری</t>
+          <t>کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مدیران تولید صنعتی | مهندسان متالورژی و مواد | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان اعتبارسنجی و صحه‌گذاری</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
